--- a/tests/example.xlsx
+++ b/tests/example.xlsx
@@ -152,14 +152,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYBERPUNK RED — «Лезвие», Кара дель Амор</t>
+          <t xml:space="preserve">CYBERPUNK RED — «Серый», Наташа Ортис</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Соло (Стрелок) • Происхождение: Бумер • €$ 610</t>
+          <t xml:space="preserve">Корпор (Иерарх) • Происхождение: Из пригорода • €$ 580</t>
         </is>
       </c>
     </row>
@@ -183,7 +183,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -233,7 +233,7 @@
         </is>
       </c>
       <c r="B10" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -253,7 +253,7 @@
         </is>
       </c>
       <c r="B12" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -263,7 +263,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -321,7 +321,7 @@
         </is>
       </c>
       <c r="B20" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -452,11 +452,11 @@
         </is>
       </c>
       <c r="D2" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+6</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="D5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D6" s="10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+5</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -577,11 +577,11 @@
         </is>
       </c>
       <c r="D7" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+5</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -652,36 +652,36 @@
         </is>
       </c>
       <c r="D10" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Боевые / Глитч</t>
+          <t xml:space="preserve">Боевые навыки</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Антитеха</t>
+          <t xml:space="preserve">Ближний бой</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECH</t>
+          <t xml:space="preserve">REF</t>
         </is>
       </c>
       <c r="D11" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+2</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подрывное дело</t>
+          <t xml:space="preserve">Антитеха</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -713,17 +713,17 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стильные навыки</t>
+          <t xml:space="preserve">Боевые / Глитч</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мода</t>
+          <t xml:space="preserve">Подрывное дело</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">EM</t>
+          <t xml:space="preserve">TECH</t>
         </is>
       </c>
       <c r="D13" s="10">
@@ -743,7 +743,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Грим</t>
+          <t xml:space="preserve">Мода</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -752,11 +752,11 @@
         </is>
       </c>
       <c r="D14" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Игра на муз. инструменте</t>
+          <t xml:space="preserve">Грим</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -777,11 +777,11 @@
         </is>
       </c>
       <c r="D15" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Выступление</t>
+          <t xml:space="preserve">Игра на муз. инструменте</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стиль</t>
+          <t xml:space="preserve">Выступление</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -827,36 +827,36 @@
         </is>
       </c>
       <c r="D17" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Навыки передвижения</t>
+          <t xml:space="preserve">Стильные навыки</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Езда на велосипеде</t>
+          <t xml:space="preserve">Стиль</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">REF</t>
+          <t xml:space="preserve">EM</t>
         </is>
       </c>
       <c r="D18" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мотоциклы</t>
+          <t xml:space="preserve">Езда на велосипеде</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -877,11 +877,11 @@
         </is>
       </c>
       <c r="D19" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пилотирование</t>
+          <t xml:space="preserve">Мотоциклы</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D20" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Верховая езда</t>
+          <t xml:space="preserve">Пилотирование</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -927,11 +927,11 @@
         </is>
       </c>
       <c r="D21" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1</t>
+          <t xml:space="preserve">+3</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ролики/скейтборд</t>
+          <t xml:space="preserve">Верховая езда</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -963,25 +963,25 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Навыки внимания</t>
+          <t xml:space="preserve">Навыки передвижения</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Внимательность</t>
+          <t xml:space="preserve">Ролики/скейтборд</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">IA</t>
+          <t xml:space="preserve">REF</t>
         </is>
       </c>
       <c r="D23" s="10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+5</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слухи Найт-Сити</t>
+          <t xml:space="preserve">Внимательность</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Криминал</t>
+          <t xml:space="preserve">Слухи Найт-Сити</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D25" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Корпорации</t>
+          <t xml:space="preserve">Криминал</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа</t>
+          <t xml:space="preserve">Корпорации</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D27" s="10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+5</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Выживание</t>
+          <t xml:space="preserve">Медиа</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -1102,28 +1102,28 @@
         </is>
       </c>
       <c r="D28" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Навыки влияния</t>
+          <t xml:space="preserve">Навыки внимания</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обаяние</t>
+          <t xml:space="preserve">Выживание</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">EM</t>
+          <t xml:space="preserve">IA</t>
         </is>
       </c>
       <c r="D29" s="10">
@@ -1138,25 +1138,25 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Навыки влияния</t>
+          <t xml:space="preserve">Навыки внимания</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Командование</t>
+          <t xml:space="preserve">Выживание</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">EM</t>
+          <t xml:space="preserve">IA</t>
         </is>
       </c>
       <c r="D30" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Связи</t>
+          <t xml:space="preserve">Обаяние</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -1177,11 +1177,11 @@
         </is>
       </c>
       <c r="D31" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Курьер</t>
+          <t xml:space="preserve">Командование</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -1202,11 +1202,11 @@
         </is>
       </c>
       <c r="D32" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+4</t>
         </is>
       </c>
     </row>
@@ -1218,20 +1218,20 @@
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Образование</t>
+          <t xml:space="preserve">Связи</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">IA</t>
+          <t xml:space="preserve">EM</t>
         </is>
       </c>
       <c r="D33" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+2</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Торг</t>
+          <t xml:space="preserve">Курьер</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Профильные знания</t>
+          <t xml:space="preserve">Образование</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -1277,11 +1277,11 @@
         </is>
       </c>
       <c r="D35" s="10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+6</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запугивание</t>
+          <t xml:space="preserve">Торг</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Знание улиц</t>
+          <t xml:space="preserve">Профильные знания</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -1327,11 +1327,11 @@
         </is>
       </c>
       <c r="D37" s="10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+5</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ложь</t>
+          <t xml:space="preserve">Запугивание</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -1352,11 +1352,11 @@
         </is>
       </c>
       <c r="D38" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -1368,70 +1368,70 @@
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Убеждение</t>
+          <t xml:space="preserve">Знание улиц</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">EM</t>
+          <t xml:space="preserve">IA</t>
         </is>
       </c>
       <c r="D39" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Технические навыки</t>
+          <t xml:space="preserve">Навыки влияния</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Базовые технические</t>
+          <t xml:space="preserve">Ложь</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECH</t>
+          <t xml:space="preserve">EM</t>
         </is>
       </c>
       <c r="D40" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Технические навыки</t>
+          <t xml:space="preserve">Навыки влияния</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Связь и кибертехника</t>
+          <t xml:space="preserve">Убеждение</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECH</t>
+          <t xml:space="preserve">EM</t>
         </is>
       </c>
       <c r="D41" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+4</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Киберимпланты и оружие</t>
+          <t xml:space="preserve">Базовые технические</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электроника</t>
+          <t xml:space="preserve">Связь и кибертехника</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Инженерное дело</t>
+          <t xml:space="preserve">Киберимпланты и оружие</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Первая помощь</t>
+          <t xml:space="preserve">Электроника</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медицина</t>
+          <t xml:space="preserve">Инженерное дело</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детектор лжи</t>
+          <t xml:space="preserve">Первая помощь</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -1577,11 +1577,11 @@
         </is>
       </c>
       <c r="D47" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Программирование</t>
+          <t xml:space="preserve">Медицина</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D48" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вскрытие сейфов</t>
+          <t xml:space="preserve">Детектор лжи</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -1643,20 +1643,70 @@
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Программирование</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TECH</t>
+        </is>
+      </c>
+      <c r="D50" s="10">
+        <v>1</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Технические навыки</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вскрытие сейфов</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TECH</t>
+        </is>
+      </c>
+      <c r="D51" s="10">
+        <v>1</v>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Технические навыки</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Торговля</t>
         </is>
       </c>
-      <c r="C50" s="0" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">TECH</t>
         </is>
       </c>
-      <c r="D50" s="10">
-        <v>0</v>
-      </c>
-      <c r="E50" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+      <c r="D52" s="10">
+        <v>1</v>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -1680,126 +1730,119 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стартовая Брутальность +1 (макс. 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 к урону дальнобойного оружия</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t xml:space="preserve">+1 к макс. уровню Авторитета</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СНАРЯЖЕНИЕ</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">СНАРЯЖЕНИЕ</t>
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дорогой костюм</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Броня лёгкая (SP 10)</t>
+          <t xml:space="preserve">Пистолет в кобуре</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пистолет с боеприпасами</t>
+          <t xml:space="preserve">Коммьютер</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Коммьютер</t>
+          <t xml:space="preserve">Кредитная карточка корпы</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нож</t>
+          <t xml:space="preserve">Портфолио</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Куртка Соло</t>
+          <t xml:space="preserve">Семейные фотографии</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Канистра топлива</t>
+          <t xml:space="preserve">Охотничий нож</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Аптечка</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Гаечный набор</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t xml:space="preserve">Рабочий комбинезон</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ЖИЗНЕННЫЙ ПУТЬ</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ЖИЗНЕННЫЙ ПУТЬ</t>
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Отношение к жизни: Нигилист: «Ничто не имеет значения»</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отношение к жизни: Циник: «Всем всё равно, кроме тех, кто платит»</t>
+          <t xml:space="preserve">То, что вы цените выше всего: Свобода делать что хочешь</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">То, что вы цените выше всего: Уважение улицы</t>
+          <t xml:space="preserve">То, чего вы боитесь: Потерять рассудок (киберпсихоз)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">То, чего вы боитесь: Скончаться в нищете и забвении</t>
+          <t xml:space="preserve">То, что вы потеряли: Работа и статус в корпорации</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">То, что вы потеряли: Семья, пропавшая в Пустоши</t>
+          <t xml:space="preserve">То, что заставляет вас вставать по утрам: Искупление прошлой ошибки</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">То, что заставляет вас вставать по утрам: Выбраться из долговой ямы</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Важный человек в вашей жизни: Долговая служба у фиксера</t>
         </is>

--- a/tests/example.xlsx
+++ b/tests/example.xlsx
@@ -152,14 +152,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYBERPUNK RED — «Серый», Наташа Ортис</t>
+          <t xml:space="preserve">CYBERPUNK RED — «Лезвие», Ингрид Сантос</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Корпор (Иерарх) • Происхождение: Из пригорода • €$ 580</t>
+          <t xml:space="preserve">Нетраннер (Соло-оператор) • Происхождение: Из пригорода • €$ 570</t>
         </is>
       </c>
     </row>
@@ -183,7 +183,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -193,7 +193,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -203,7 +203,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -213,7 +213,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -223,7 +223,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -233,7 +233,7 @@
         </is>
       </c>
       <c r="B10" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -243,7 +243,7 @@
         </is>
       </c>
       <c r="B11" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -253,7 +253,7 @@
         </is>
       </c>
       <c r="B12" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -273,7 +273,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15"/>
@@ -291,7 +291,7 @@
         </is>
       </c>
       <c r="B17" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -301,7 +301,7 @@
         </is>
       </c>
       <c r="B18" s="6">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="B19" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -321,7 +321,7 @@
         </is>
       </c>
       <c r="B20" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -331,7 +331,7 @@
         </is>
       </c>
       <c r="B21" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="B22" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -351,7 +351,7 @@
         </is>
       </c>
       <c r="B23" s="6">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -361,7 +361,7 @@
         </is>
       </c>
       <c r="B24" s="6">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="B25" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -381,7 +381,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -391,7 +391,7 @@
         </is>
       </c>
       <c r="B27" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="D3" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -652,11 +652,11 @@
         </is>
       </c>
       <c r="D10" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -677,11 +677,11 @@
         </is>
       </c>
       <c r="D11" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -802,11 +802,11 @@
         </is>
       </c>
       <c r="D16" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -827,11 +827,11 @@
         </is>
       </c>
       <c r="D17" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+3</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -877,11 +877,11 @@
         </is>
       </c>
       <c r="D19" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D20" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -927,11 +927,11 @@
         </is>
       </c>
       <c r="D21" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+3</t>
+          <t xml:space="preserve">+2</t>
         </is>
       </c>
     </row>
@@ -952,11 +952,11 @@
         </is>
       </c>
       <c r="D22" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -977,11 +977,11 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -1002,11 +1002,11 @@
         </is>
       </c>
       <c r="D24" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+2</t>
         </is>
       </c>
     </row>
@@ -1052,11 +1052,11 @@
         </is>
       </c>
       <c r="D26" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1</t>
+          <t xml:space="preserve">+2</t>
         </is>
       </c>
     </row>
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D27" s="10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+5</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -1102,11 +1102,11 @@
         </is>
       </c>
       <c r="D28" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -1202,11 +1202,11 @@
         </is>
       </c>
       <c r="D32" s="10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+4</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D34" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -1277,11 +1277,11 @@
         </is>
       </c>
       <c r="D35" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+6</t>
+          <t xml:space="preserve">+2</t>
         </is>
       </c>
     </row>
@@ -1327,11 +1327,11 @@
         </is>
       </c>
       <c r="D37" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+5</t>
+          <t xml:space="preserve">+2</t>
         </is>
       </c>
     </row>
@@ -1352,11 +1352,11 @@
         </is>
       </c>
       <c r="D38" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="D41" s="10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+4</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
@@ -1452,11 +1452,11 @@
         </is>
       </c>
       <c r="D42" s="10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+6</t>
         </is>
       </c>
     </row>
@@ -1477,11 +1477,11 @@
         </is>
       </c>
       <c r="D43" s="10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+5</t>
         </is>
       </c>
     </row>
@@ -1527,11 +1527,11 @@
         </is>
       </c>
       <c r="D45" s="10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+6</t>
         </is>
       </c>
     </row>
@@ -1552,11 +1552,11 @@
         </is>
       </c>
       <c r="D46" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D48" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">+1</t>
         </is>
       </c>
     </row>
@@ -1652,11 +1652,11 @@
         </is>
       </c>
       <c r="D50" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1</t>
+          <t xml:space="preserve">+6</t>
         </is>
       </c>
     </row>
@@ -1677,11 +1677,11 @@
         </is>
       </c>
       <c r="D51" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1</t>
+          <t xml:space="preserve">+2</t>
         </is>
       </c>
     </row>
@@ -1702,11 +1702,11 @@
         </is>
       </c>
       <c r="D52" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1</t>
+          <t xml:space="preserve">+3</t>
         </is>
       </c>
     </row>
@@ -1730,121 +1730,135 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 к макс. уровню Авторитета</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t xml:space="preserve">Особость Нетраннера: Interface (INT + Interface Check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+1 к макс. глубине Сети</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Работает один: сам чинит свою деку</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">СНАРЯЖЕНИЕ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Дорогой костюм</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Пистолет в кобуре</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Коммьютер</t>
+          <t xml:space="preserve">Кибердека (доступ в Сеть)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кредитная карточка корпы</t>
+          <t xml:space="preserve">Усилитель сигнала</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портфолио</t>
+          <t xml:space="preserve">Коммьютер</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Семейные фотографии</t>
+          <t xml:space="preserve">Лёгкая броня</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Охотничий нож</t>
+          <t xml:space="preserve">Очки AR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Семейные фотографии</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Охотничий нож</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Рабочий комбинезон</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ЖИЗНЕННЫЙ ПУТЬ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Отношение к жизни: Нигилист: «Ничто не имеет значения»</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">То, что вы цените выше всего: Свобода делать что хочешь</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">То, чего вы боитесь: Потерять рассудок (киберпсихоз)</t>
+          <t xml:space="preserve">Отношение к жизни: Романтик: «Каждый день — история, которую стоит рассказать»</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">То, что вы потеряли: Работа и статус в корпорации</t>
+          <t xml:space="preserve">То, что вы цените выше всего: Свобода делать что хочешь</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">То, что заставляет вас вставать по утрам: Искупление прошлой ошибки</t>
+          <t xml:space="preserve">То, чего вы боитесь: Предательство близких</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Важный человек в вашей жизни: Долговая служба у фиксера</t>
+          <t xml:space="preserve">То, что вы потеряли: Семья, пропавшая в Пустоши</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">То, что заставляет вас вставать по утрам: Найти пропавшего(ую)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Важный человек в вашей жизни: Случайный свидетель вашего секрета</t>
         </is>
       </c>
     </row>
